--- a/Docs/OATH_VALUE_REVERSE_TABLE.xlsx
+++ b/Docs/OATH_VALUE_REVERSE_TABLE.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gustj\Documents\GitHub\dnf-hell-optimizer-react\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\users\gustj\documents\github\dnf-hell-optimizer-react\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FAD205-FB3F-4C31-86A6-C4C92D886EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3184387-697D-4479-8048-40203A3E0885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="장비 세트 단계" sheetId="1" r:id="rId1"/>
     <sheet name="서약 세트 단계" sheetId="2" r:id="rId2"/>
-    <sheet name="무기" sheetId="8" r:id="rId3"/>
-    <sheet name="장비 등급별 옵션" sheetId="3" r:id="rId4"/>
-    <sheet name="무기 등급별 옵션" sheetId="9" r:id="rId5"/>
-    <sheet name="서약의 가호" sheetId="4" r:id="rId6"/>
-    <sheet name="서약 등급별 최종데미지" sheetId="5" r:id="rId7"/>
-    <sheet name="입력 규칙" sheetId="6" r:id="rId8"/>
-    <sheet name="역산 기준" sheetId="7" r:id="rId9"/>
+    <sheet name="무기" sheetId="3" r:id="rId3"/>
+    <sheet name="장비 등급별 옵션" sheetId="4" r:id="rId4"/>
+    <sheet name="무기 등급별 옵션" sheetId="5" r:id="rId5"/>
+    <sheet name="서약의 가호" sheetId="6" r:id="rId6"/>
+    <sheet name="서약 등급별 최종데미지" sheetId="7" r:id="rId7"/>
+    <sheet name="입력 규칙" sheetId="8" r:id="rId8"/>
+    <sheet name="역산 기준" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'서약 세트 단계'!$A$1:$J$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'서약의 가호'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역산 기준'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'장비 세트 단계'!$A$1:$AF$22</definedName>
     <definedName name="Equip_Belt_Grades">'장비 등급별 옵션'!$A$30:$A$34</definedName>
     <definedName name="Equip_Bracelet_Grades">'장비 등급별 옵션'!$J$16:$J$20</definedName>
     <definedName name="Equip_Earring_Grades">'장비 등급별 옵션'!$J$37:$J$40</definedName>
@@ -56,12 +57,80 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>레어 I 기준값을 앵커로 환산한 세트포인트 단계의 절대 최종 데미지.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>현재 장비점수 공통식에 확정된 쿨감 환산식이 없어 참고값으로만 둔다.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>공식 장비점수 전후비에서 장비 본체, 공격력 증가, 주스탯 전후비를 제거한 세트 단계 배율.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>직업별 기본 스탯. 현재 표본 마키듀얼은 힘 779.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>절대 세트 최종뎀 역산의 기준값. 확인값이 바뀌면 이 셀만 수정한다.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="131">
   <si>
     <t>세트단계</t>
   </si>
   <si>
+    <t>필요 세트포인트</t>
+  </si>
+  <si>
     <t>변경 후 장비점수</t>
   </si>
   <si>
@@ -104,165 +173,201 @@
     <t>공격력증가</t>
   </si>
   <si>
+    <t>이전 단계 전후비(%)</t>
+  </si>
+  <si>
+    <t>세트 단계 최종뎀(%)</t>
+  </si>
+  <si>
+    <t>장비최종뎀곱</t>
+  </si>
+  <si>
+    <t>장비공격력증가합</t>
+  </si>
+  <si>
+    <t>장비속강합</t>
+  </si>
+  <si>
+    <t>장비쿨감합(참고)</t>
+  </si>
+  <si>
+    <t>장비힘합</t>
+  </si>
+  <si>
+    <t>장비본체옵션전후비</t>
+  </si>
+  <si>
+    <t>공격력증가전후비</t>
+  </si>
+  <si>
+    <t>주스탯전후비</t>
+  </si>
+  <si>
+    <t>세트제외보정점수</t>
+  </si>
+  <si>
+    <t>전체점수전후비</t>
+  </si>
+  <si>
+    <t>세트단계전후비</t>
+  </si>
+  <si>
+    <t>최종뎀 0.1% 반올림</t>
+  </si>
+  <si>
+    <t>검산 장비점수</t>
+  </si>
+  <si>
+    <t>검산 오차</t>
+  </si>
+  <si>
+    <t>레어 I</t>
+  </si>
+  <si>
+    <t>유니크</t>
+  </si>
+  <si>
+    <t>레어</t>
+  </si>
+  <si>
+    <t>레어 II</t>
+  </si>
+  <si>
+    <t>레어 III</t>
+  </si>
+  <si>
+    <t>레어 IV</t>
+  </si>
+  <si>
+    <t>레어 V</t>
+  </si>
+  <si>
+    <t>유니크 I</t>
+  </si>
+  <si>
+    <t>유니크 II</t>
+  </si>
+  <si>
+    <t>레전더리</t>
+  </si>
+  <si>
+    <t>유니크 III</t>
+  </si>
+  <si>
+    <t>유니크 IV</t>
+  </si>
+  <si>
+    <t>유니크 V</t>
+  </si>
+  <si>
+    <t>레전더리 I</t>
+  </si>
+  <si>
+    <t>레전더리 II</t>
+  </si>
+  <si>
+    <t>레전더리 III</t>
+  </si>
+  <si>
+    <t>에픽</t>
+  </si>
+  <si>
+    <t>레전더리 IV</t>
+  </si>
+  <si>
+    <t>레전더리 V</t>
+  </si>
+  <si>
+    <t>에픽 I</t>
+  </si>
+  <si>
+    <t>에픽 II</t>
+  </si>
+  <si>
+    <t>에픽 III</t>
+  </si>
+  <si>
+    <t>에픽 IV</t>
+  </si>
+  <si>
+    <t>에픽 V</t>
+  </si>
+  <si>
+    <t>태초</t>
+  </si>
+  <si>
+    <t>에픽잠식(업글)</t>
+  </si>
+  <si>
+    <t>기준 캐릭터</t>
+  </si>
+  <si>
+    <t>기준 세트포인트(자동)</t>
+  </si>
+  <si>
+    <t>기준 장비점수</t>
+  </si>
+  <si>
+    <t>기준스탯</t>
+  </si>
+  <si>
+    <t>기준 직업 기본스탯</t>
+  </si>
+  <si>
+    <t>레어 I 기준 세트 최종뎀(%)</t>
+  </si>
+  <si>
+    <t>마키듀얼</t>
+  </si>
+  <si>
+    <t>기준 총 공격력증가</t>
+  </si>
+  <si>
+    <t>필요세트포인트</t>
+  </si>
+  <si>
+    <t>변경 후 세트포인트</t>
+  </si>
+  <si>
+    <t>서약 등급</t>
+  </si>
+  <si>
+    <t>레어 결정</t>
+  </si>
+  <si>
+    <t>유니크 결정</t>
+  </si>
+  <si>
+    <t>레전 결정</t>
+  </si>
+  <si>
+    <t>에픽 결정</t>
+  </si>
+  <si>
+    <t>태초 결정</t>
+  </si>
+  <si>
     <t>단계 증가량(%)</t>
   </si>
   <si>
     <t>누적 증가량(%)</t>
   </si>
   <si>
-    <t>장비최종뎀곱</t>
-  </si>
-  <si>
-    <t>장비공격력증가합</t>
-  </si>
-  <si>
-    <t>장비속강합</t>
-  </si>
-  <si>
-    <t>장비쿨감합</t>
-  </si>
-  <si>
-    <t>장비힘합</t>
-  </si>
-  <si>
-    <t>장비옵션배율</t>
-  </si>
-  <si>
-    <t>공격력증가배율</t>
-  </si>
-  <si>
-    <t>스탯전후비(제거)</t>
+    <t>결정배율</t>
+  </si>
+  <si>
+    <t>서약등급배율</t>
+  </si>
+  <si>
+    <t>가호최종뎀배율</t>
+  </si>
+  <si>
+    <t>서약스탯배율</t>
   </si>
   <si>
     <t>보정점수</t>
   </si>
   <si>
-    <t>레어 I</t>
-  </si>
-  <si>
-    <t>유니크</t>
-  </si>
-  <si>
-    <t>레어</t>
-  </si>
-  <si>
-    <t>레어 II</t>
-  </si>
-  <si>
-    <t>레어 III</t>
-  </si>
-  <si>
-    <t>레어 IV</t>
-  </si>
-  <si>
-    <t>레어 V</t>
-  </si>
-  <si>
-    <t>유니크 I</t>
-  </si>
-  <si>
-    <t>유니크 II</t>
-  </si>
-  <si>
-    <t>레전더리</t>
-  </si>
-  <si>
-    <t>유니크 III</t>
-  </si>
-  <si>
-    <t>유니크 IV</t>
-  </si>
-  <si>
-    <t>유니크 V</t>
-  </si>
-  <si>
-    <t>레전더리 I</t>
-  </si>
-  <si>
-    <t>레전더리 II</t>
-  </si>
-  <si>
-    <t>레전더리 III</t>
-  </si>
-  <si>
-    <t>에픽</t>
-  </si>
-  <si>
-    <t>레전더리 IV</t>
-  </si>
-  <si>
-    <t>레전더리 V</t>
-  </si>
-  <si>
-    <t>에픽 I</t>
-  </si>
-  <si>
-    <t>에픽 II</t>
-  </si>
-  <si>
-    <t>에픽 III</t>
-  </si>
-  <si>
-    <t>에픽 IV</t>
-  </si>
-  <si>
-    <t>에픽 V</t>
-  </si>
-  <si>
-    <t>태초</t>
-  </si>
-  <si>
-    <t>에픽잠식(업글)</t>
-  </si>
-  <si>
-    <t>기준 캐릭터</t>
-  </si>
-  <si>
-    <t>기준 장비점수</t>
-  </si>
-  <si>
-    <t>기준스탯</t>
-  </si>
-  <si>
-    <t>마키듀얼</t>
-  </si>
-  <si>
-    <t>기준 총 공격력증가</t>
-  </si>
-  <si>
-    <t>변경 후 세트포인트</t>
-  </si>
-  <si>
-    <t>서약 등급</t>
-  </si>
-  <si>
-    <t>레어 결정</t>
-  </si>
-  <si>
-    <t>유니크 결정</t>
-  </si>
-  <si>
-    <t>레전 결정</t>
-  </si>
-  <si>
-    <t>에픽 결정</t>
-  </si>
-  <si>
-    <t>태초 결정</t>
-  </si>
-  <si>
-    <t>결정배율</t>
-  </si>
-  <si>
-    <t>서약등급배율</t>
-  </si>
-  <si>
-    <t>가호최종뎀배율</t>
-  </si>
-  <si>
-    <t>서약스탯배율</t>
-  </si>
-  <si>
     <t>기준 서약 포인트</t>
   </si>
   <si>
@@ -293,6 +398,9 @@
     <t>쿨타임감소</t>
   </si>
   <si>
+    <t>세트포인트(통일)</t>
+  </si>
+  <si>
     <t>가호 단계/이름</t>
   </si>
   <si>
@@ -408,42 +516,6 @@
   </si>
   <si>
     <t>세트 외 옵션 변화가 없으면 1</t>
-  </si>
-  <si>
-    <t>세트포인트(통일)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>레어</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>유니크</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>레전더리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>에픽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>태초</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>에픽잠식(업글)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>필요세트포인트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>필요 세트포인트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -895,8 +967,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -908,102 +980,124 @@
     <col min="7" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="17" max="17" width="20" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="14" customWidth="1"/>
-    <col min="25" max="25" width="16" customWidth="1"/>
-    <col min="26" max="27" width="18" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="21" customWidth="1"/>
+    <col min="25" max="25" width="20" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="19" customWidth="1"/>
+    <col min="28" max="29" width="18" customWidth="1"/>
+    <col min="30" max="30" width="21" customWidth="1"/>
+    <col min="31" max="31" width="17" customWidth="1"/>
+    <col min="32" max="32" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="16.5" customHeight="1">
+    <row r="1" spans="1:32" ht="16.5" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="16.5" customHeight="1">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="16.5" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B2" s="10">
         <v>750</v>
@@ -1016,47 +1110,47 @@
         <v>6306</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P2" s="10">
         <v>0</v>
       </c>
-      <c r="Q2" s="15">
+      <c r="Q2" s="16">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="R2" s="15">
-        <f t="shared" ref="R2:R22" si="1">IF(OR(AA2="",$AA$2=""),"",(AA2/$AA$2*1.04-1)*100)</f>
+      <c r="R2" s="16">
+        <f t="shared" ref="R2:R22" si="1">IF(OR(AC2="",$AC$2="",$R$25=""),"",(AC2/$AC$2*(1+$R$25/100)-1)*100)</f>
         <v>4.0000000000000036</v>
       </c>
       <c r="S2" s="15">
@@ -1080,25 +1174,45 @@
         <v>1572</v>
       </c>
       <c r="X2" s="16">
-        <f t="shared" ref="X2:X22" si="2">(S2*((1.05+U2*0.0045)/(1.05))*IF(V2&gt;=100,1E+99,100/(100-V2)))/($S$25*((1.05+$U$25*0.0045)/(1.05))*IF($V$25&gt;=100,1E+99,100/(100-$V$25)))</f>
+        <f t="shared" ref="X2:X22" si="2">(S2*((1.05+U2*0.0045)/1.05))/($S$25*((1.05+$U$25*0.0045)/1.05))</f>
         <v>0.50984421002837466</v>
       </c>
       <c r="Y2" s="16">
-        <f t="shared" ref="Y2:Y22" si="3">IF($C$27="",1,(1+($C$27+T2-$T$25-$P$25+P2)/100)/(1+$C$27/100))</f>
+        <f t="shared" ref="Y2:Y22" si="3">IF($C$27="","",(1+($C$27+T2-$T$25+P2-$P$25)/100)/(1+$C$27/100))</f>
         <v>0.68264423347002978</v>
       </c>
       <c r="Z2" s="16">
-        <f t="shared" ref="Z2:Z22" si="4">IF(OR(D2="",$D$25=""),"",(1+(D2+168350+297900+INT(3.08*(D2-779)+2886))/250)/(1+($D$25+168350+297900+INT(3.08*($D$25-779)+2886))/250))</f>
+        <f t="shared" ref="Z2:Z22" si="4">IF(OR(D2="",$D$25="",$Q$25=""),"",(1+(D2+168350+297900+TRUNC(3.08*(D2-$Q$25)+2886))/250)/(1+($D$25+168350+297900+TRUNC(3.08*($D$25-$Q$25)+2886))/250))</f>
         <v>0.9987857632258561</v>
       </c>
       <c r="AA2" s="15">
-        <f t="shared" ref="AA2:AA22" si="5">IF(Z2="","",C2/X2/Y2/Z2)</f>
+        <f t="shared" ref="AA2:AA22" si="5">IF(OR(C2="",X2="",Y2="",Z2=""),"",C2/X2/Y2/Z2)</f>
         <v>2068.3528521382154</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB2" s="16">
+        <f t="shared" ref="AB2:AB22" si="6">IF(OR(C2="",$C$25=""),"",C2/$C$25)</f>
+        <v>5.2646994215420663E-2</v>
+      </c>
+      <c r="AC2" s="16">
+        <f t="shared" ref="AC2:AC22" si="7">IF(OR(AB2="",X2="",Y2="",Z2=""),"",AB2/X2/Y2/Z2)</f>
+        <v>0.15145001480107018</v>
+      </c>
+      <c r="AD2" s="16">
+        <f t="shared" ref="AD2:AD22" si="8">IF(R2="","",ROUND(R2,1))</f>
+        <v>4</v>
+      </c>
+      <c r="AE2" s="14">
+        <f t="shared" ref="AE2:AE22" si="9">IF(OR($C$25="",X2="",Y2="",Z2="",AC2=""),"",ROUND($C$25*X2*Y2*Z2*AC2,0))</f>
+        <v>719</v>
+      </c>
+      <c r="AF2" s="14">
+        <f t="shared" ref="AF2:AF22" si="10">IF(OR(AE2="",C2=""),"",AE2-C2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="16.5" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" s="10">
         <v>830</v>
@@ -1111,46 +1225,46 @@
         <v>6306</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P3" s="10">
         <v>0</v>
       </c>
-      <c r="Q3" s="15">
-        <f>IF(OR(AA3="",AA2=""),"",(AA3/AA2-1)*100)</f>
+      <c r="Q3" s="16">
+        <f t="shared" ref="Q3:Q22" si="11">IF(OR(R3="",R2=""),"",((1+R3/100)/(1+R2/100)-1)*100)</f>
         <v>3.8942976356050041</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="16">
         <f t="shared" si="1"/>
         <v>8.0500695410292025</v>
       </c>
@@ -1190,10 +1304,30 @@
         <f t="shared" si="5"/>
         <v>2148.9006683550028</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB3" s="16">
+        <f t="shared" si="6"/>
+        <v>5.4697224866368896E-2</v>
+      </c>
+      <c r="AC3" s="16">
+        <f t="shared" si="7"/>
+        <v>0.15734792914659168</v>
+      </c>
+      <c r="AD3" s="16">
+        <f t="shared" si="8"/>
+        <v>8.1</v>
+      </c>
+      <c r="AE3" s="14">
+        <f t="shared" si="9"/>
+        <v>747</v>
+      </c>
+      <c r="AF3" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="16.5" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" s="10">
         <v>910</v>
@@ -1206,47 +1340,47 @@
         <v>6306</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P4" s="10">
         <v>0</v>
       </c>
-      <c r="Q4" s="15">
-        <f t="shared" ref="Q4:Q22" si="6">IF(OR(AA4="",AA3=""),"",(AA4/AA3-1)*100)</f>
-        <v>3.7483266398928849</v>
-      </c>
-      <c r="R4" s="15">
-        <f>IF(OR(AA4="",$AA$2=""),"",(AA4/$AA$2*1.04-1)*100)</f>
+      <c r="Q4" s="16">
+        <f t="shared" si="11"/>
+        <v>3.7483266398929072</v>
+      </c>
+      <c r="R4" s="16">
+        <f t="shared" si="1"/>
         <v>12.100139082058403</v>
       </c>
       <c r="S4" s="15">
@@ -1285,10 +1419,30 @@
         <f t="shared" si="5"/>
         <v>2229.4484845717898</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB4" s="16">
+        <f t="shared" si="6"/>
+        <v>5.6747455517317129E-2</v>
+      </c>
+      <c r="AC4" s="16">
+        <f t="shared" si="7"/>
+        <v>0.16324584349211319</v>
+      </c>
+      <c r="AD4" s="16">
+        <f t="shared" si="8"/>
+        <v>12.1</v>
+      </c>
+      <c r="AE4" s="14">
+        <f t="shared" si="9"/>
+        <v>775</v>
+      </c>
+      <c r="AF4" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="16.5" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B5" s="10">
         <v>990</v>
@@ -1301,48 +1455,48 @@
         <v>6306</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P5" s="10">
         <v>0</v>
       </c>
-      <c r="Q5" s="15">
-        <f t="shared" si="6"/>
-        <v>3.4838709677419422</v>
-      </c>
-      <c r="R5" s="15">
+      <c r="Q5" s="16">
+        <f t="shared" si="11"/>
+        <v>3.48387096774192</v>
+      </c>
+      <c r="R5" s="16">
         <f t="shared" si="1"/>
-        <v>16.005563282336578</v>
+        <v>16.005563282336553</v>
       </c>
       <c r="S5" s="15">
         <f>(1+IFERROR(VLOOKUP(E5,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F5,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G5,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H5,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I5,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J5,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K5,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L5,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M5,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N5,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O5,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -1380,10 +1534,30 @@
         <f t="shared" si="5"/>
         <v>2307.119593066549</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB5" s="16">
+        <f t="shared" si="6"/>
+        <v>5.8724463645017204E-2</v>
+      </c>
+      <c r="AC5" s="16">
+        <f t="shared" si="7"/>
+        <v>0.16893311803958033</v>
+      </c>
+      <c r="AD5" s="16">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="AE5" s="14">
+        <f t="shared" si="9"/>
+        <v>802</v>
+      </c>
+      <c r="AF5" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="16.5" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6" s="10">
         <v>1070</v>
@@ -1396,48 +1570,48 @@
         <v>6306</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P6" s="10">
         <v>0</v>
       </c>
-      <c r="Q6" s="15">
-        <f t="shared" si="6"/>
+      <c r="Q6" s="16">
+        <f t="shared" si="11"/>
         <v>3.4912718204488824</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="16">
         <f t="shared" si="1"/>
-        <v>20.055632823365798</v>
+        <v>20.055632823365777</v>
       </c>
       <c r="S6" s="15">
         <f>(1+IFERROR(VLOOKUP(E6,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F6,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G6,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H6,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I6,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J6,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K6,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L6,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M6,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N6,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O6,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -1475,10 +1649,30 @@
         <f t="shared" si="5"/>
         <v>2387.6674092833364</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB6" s="16">
+        <f t="shared" si="6"/>
+        <v>6.0774694295965437E-2</v>
+      </c>
+      <c r="AC6" s="16">
+        <f t="shared" si="7"/>
+        <v>0.17483103238510186</v>
+      </c>
+      <c r="AD6" s="16">
+        <f t="shared" si="8"/>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="AE6" s="14">
+        <f t="shared" si="9"/>
+        <v>830</v>
+      </c>
+      <c r="AF6" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="16.5" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" s="10">
         <v>1200</v>
@@ -1491,46 +1685,46 @@
         <v>6322</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P7" s="10">
         <v>0</v>
       </c>
-      <c r="Q7" s="15">
-        <f t="shared" si="6"/>
-        <v>23.480211457866716</v>
-      </c>
-      <c r="R7" s="15">
+      <c r="Q7" s="16">
+        <f t="shared" si="11"/>
+        <v>23.480211457866741</v>
+      </c>
+      <c r="R7" s="16">
         <f t="shared" si="1"/>
         <v>48.244949277372129</v>
       </c>
@@ -1570,10 +1764,30 @@
         <f t="shared" si="5"/>
         <v>2948.2967658936318</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB7" s="16">
+        <f t="shared" si="6"/>
+        <v>0.10778355422127847</v>
+      </c>
+      <c r="AC7" s="16">
+        <f t="shared" si="7"/>
+        <v>0.21588172848309525</v>
+      </c>
+      <c r="AD7" s="16">
+        <f t="shared" si="8"/>
+        <v>48.2</v>
+      </c>
+      <c r="AE7" s="14">
+        <f t="shared" si="9"/>
+        <v>1472</v>
+      </c>
+      <c r="AF7" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="16.5" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" s="10">
         <v>1285</v>
@@ -1586,48 +1800,48 @@
         <v>6326</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P8" s="10">
         <v>433</v>
       </c>
-      <c r="Q8" s="15">
-        <f t="shared" si="6"/>
-        <v>6.7796793757492591</v>
-      </c>
-      <c r="R8" s="15">
+      <c r="Q8" s="16">
+        <f t="shared" si="11"/>
+        <v>6.7796793757492813</v>
+      </c>
+      <c r="R8" s="16">
         <f t="shared" si="1"/>
-        <v>58.295481529120075</v>
+        <v>58.295481529120096</v>
       </c>
       <c r="S8" s="15">
         <f>(1+IFERROR(VLOOKUP(E8,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F8,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G8,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H8,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I8,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J8,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K8,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L8,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M8,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N8,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O8,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -1665,10 +1879,30 @@
         <f t="shared" si="5"/>
         <v>3148.1818336668048</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB8" s="16">
+        <f t="shared" si="6"/>
+        <v>0.13040931390495716</v>
+      </c>
+      <c r="AC8" s="16">
+        <f t="shared" si="7"/>
+        <v>0.23051781750507469</v>
+      </c>
+      <c r="AD8" s="16">
+        <f t="shared" si="8"/>
+        <v>58.3</v>
+      </c>
+      <c r="AE8" s="14">
+        <f t="shared" si="9"/>
+        <v>1781</v>
+      </c>
+      <c r="AF8" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="16.5" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" s="10">
         <v>1370</v>
@@ -1681,48 +1915,48 @@
         <v>6328</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P9" s="10">
         <v>1299</v>
       </c>
-      <c r="Q9" s="15">
-        <f t="shared" si="6"/>
-        <v>13.822436013014938</v>
-      </c>
-      <c r="R9" s="15">
+      <c r="Q9" s="16">
+        <f t="shared" si="11"/>
+        <v>13.822436013014915</v>
+      </c>
+      <c r="R9" s="16">
         <f t="shared" si="1"/>
-        <v>80.17577317497657</v>
+        <v>80.175773174976555</v>
       </c>
       <c r="S9" s="15">
         <f>(1+IFERROR(VLOOKUP(E9,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F9,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G9,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H9,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I9,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J9,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K9,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L9,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M9,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N9,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O9,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -1746,7 +1980,7 @@
       </c>
       <c r="X9" s="16">
         <f t="shared" si="2"/>
-        <v>0.68675741238601551</v>
+        <v>0.68675741238601562</v>
       </c>
       <c r="Y9" s="16">
         <f t="shared" si="3"/>
@@ -1758,12 +1992,32 @@
       </c>
       <c r="AA9" s="15">
         <f t="shared" si="5"/>
-        <v>3583.3372531987593</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="16.5" customHeight="1">
+        <v>3583.3372531987584</v>
+      </c>
+      <c r="AB9" s="16">
+        <f t="shared" si="6"/>
+        <v>0.15369407629786921</v>
+      </c>
+      <c r="AC9" s="16">
+        <f t="shared" si="7"/>
+        <v>0.26238099532831211</v>
+      </c>
+      <c r="AD9" s="16">
+        <f t="shared" si="8"/>
+        <v>80.2</v>
+      </c>
+      <c r="AE9" s="14">
+        <f t="shared" si="9"/>
+        <v>2099</v>
+      </c>
+      <c r="AF9" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="16.5" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B10" s="10">
         <v>1455</v>
@@ -1776,46 +2030,46 @@
         <v>6329</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P10" s="10">
         <v>1732</v>
       </c>
-      <c r="Q10" s="15">
-        <f t="shared" si="6"/>
-        <v>11.512792938484285</v>
-      </c>
-      <c r="R10" s="15">
+      <c r="Q10" s="16">
+        <f t="shared" si="11"/>
+        <v>11.512792938484306</v>
+      </c>
+      <c r="R10" s="16">
         <f t="shared" si="1"/>
         <v>100.91903686592474</v>
       </c>
@@ -1855,10 +2109,30 @@
         <f t="shared" si="5"/>
         <v>3995.8794514471028</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB10" s="16">
+        <f t="shared" si="6"/>
+        <v>0.17441605037709598</v>
+      </c>
+      <c r="AC10" s="16">
+        <f t="shared" si="7"/>
+        <v>0.29258837603039484</v>
+      </c>
+      <c r="AD10" s="16">
+        <f t="shared" si="8"/>
+        <v>100.9</v>
+      </c>
+      <c r="AE10" s="14">
+        <f t="shared" si="9"/>
+        <v>2382</v>
+      </c>
+      <c r="AF10" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="16.5" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B11" s="10">
         <v>1540</v>
@@ -1871,46 +2145,46 @@
         <v>6330</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P11" s="10">
         <v>2598</v>
       </c>
-      <c r="Q11" s="15">
-        <f t="shared" si="6"/>
+      <c r="Q11" s="16">
+        <f t="shared" si="11"/>
         <v>11.493441686450478</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="16">
         <f t="shared" si="1"/>
         <v>124.01154920508772</v>
       </c>
@@ -1950,10 +2224,30 @@
         <f t="shared" si="5"/>
         <v>4455.1435260600329</v>
       </c>
-    </row>
-    <row r="12" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB11" s="16">
+        <f t="shared" si="6"/>
+        <v>0.20136193893241561</v>
+      </c>
+      <c r="AC11" s="16">
+        <f t="shared" si="7"/>
+        <v>0.32621685041078075</v>
+      </c>
+      <c r="AD11" s="16">
+        <f t="shared" si="8"/>
+        <v>124</v>
+      </c>
+      <c r="AE11" s="14">
+        <f t="shared" si="9"/>
+        <v>2750</v>
+      </c>
+      <c r="AF11" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="16.5" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B12" s="10">
         <v>1650</v>
@@ -1966,46 +2260,46 @@
         <v>6333</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P12" s="10">
         <v>3464</v>
       </c>
-      <c r="Q12" s="15">
-        <f t="shared" si="6"/>
-        <v>27.529839143175305</v>
-      </c>
-      <c r="R12" s="15">
+      <c r="Q12" s="16">
+        <f t="shared" si="11"/>
+        <v>27.529839143175327</v>
+      </c>
+      <c r="R12" s="16">
         <f t="shared" si="1"/>
         <v>185.68156836338341</v>
       </c>
@@ -2031,7 +2325,7 @@
       </c>
       <c r="X12" s="16">
         <f t="shared" si="2"/>
-        <v>0.72346282794358729</v>
+        <v>0.72346282794358718</v>
       </c>
       <c r="Y12" s="16">
         <f t="shared" si="3"/>
@@ -2043,12 +2337,32 @@
       </c>
       <c r="AA12" s="15">
         <f t="shared" si="5"/>
-        <v>5681.6373723819479</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="16.5" customHeight="1">
+        <v>5681.6373723819488</v>
+      </c>
+      <c r="AB12" s="16">
+        <f t="shared" si="6"/>
+        <v>0.26587098191403674</v>
+      </c>
+      <c r="AC12" s="16">
+        <f t="shared" si="7"/>
+        <v>0.41602382458680154</v>
+      </c>
+      <c r="AD12" s="16">
+        <f t="shared" si="8"/>
+        <v>185.7</v>
+      </c>
+      <c r="AE12" s="14">
+        <f t="shared" si="9"/>
+        <v>3631</v>
+      </c>
+      <c r="AF12" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="16.5" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B13" s="10">
         <v>1735</v>
@@ -2061,46 +2375,46 @@
         <v>6336</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P13" s="10">
         <v>4330</v>
       </c>
-      <c r="Q13" s="15">
-        <f t="shared" si="6"/>
+      <c r="Q13" s="16">
+        <f t="shared" si="11"/>
         <v>8.8595634952846058</v>
       </c>
-      <c r="R13" s="15">
+      <c r="R13" s="16">
         <f t="shared" si="1"/>
         <v>210.99170830686225</v>
       </c>
@@ -2140,10 +2454,30 @@
         <f t="shared" si="5"/>
         <v>6185.0056429599463</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB13" s="16">
+        <f t="shared" si="6"/>
+        <v>0.29962656513143443</v>
+      </c>
+      <c r="AC13" s="16">
+        <f t="shared" si="7"/>
+        <v>0.45288171948158062</v>
+      </c>
+      <c r="AD13" s="16">
+        <f t="shared" si="8"/>
+        <v>211</v>
+      </c>
+      <c r="AE13" s="14">
+        <f t="shared" si="9"/>
+        <v>4092</v>
+      </c>
+      <c r="AF13" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="16.5" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B14" s="10">
         <v>1820</v>
@@ -2156,46 +2490,46 @@
         <v>6389</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P14" s="10">
         <v>5247</v>
       </c>
-      <c r="Q14" s="15">
-        <f t="shared" si="6"/>
-        <v>8.503066142034843</v>
-      </c>
-      <c r="R14" s="15">
+      <c r="Q14" s="16">
+        <f t="shared" si="11"/>
+        <v>8.5030661420348217</v>
+      </c>
+      <c r="R14" s="16">
         <f t="shared" si="1"/>
         <v>237.43553896043875</v>
       </c>
@@ -2235,10 +2569,30 @@
         <f t="shared" si="5"/>
         <v>6710.9207636694173</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB14" s="16">
+        <f t="shared" si="6"/>
+        <v>0.33660393937175076</v>
+      </c>
+      <c r="AC14" s="16">
+        <f t="shared" si="7"/>
+        <v>0.49139055163428402</v>
+      </c>
+      <c r="AD14" s="16">
+        <f t="shared" si="8"/>
+        <v>237.4</v>
+      </c>
+      <c r="AE14" s="14">
+        <f t="shared" si="9"/>
+        <v>4597</v>
+      </c>
+      <c r="AF14" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="16.5" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B15" s="10">
         <v>1905</v>
@@ -2251,48 +2605,48 @@
         <v>6390</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P15" s="10">
         <v>5731</v>
       </c>
-      <c r="Q15" s="15">
-        <f t="shared" si="6"/>
-        <v>7.0821532873021509</v>
-      </c>
-      <c r="R15" s="15">
+      <c r="Q15" s="16">
+        <f t="shared" si="11"/>
+        <v>7.0821532873021287</v>
+      </c>
+      <c r="R15" s="16">
         <f t="shared" si="1"/>
-        <v>261.33324107545116</v>
+        <v>261.3332410754511</v>
       </c>
       <c r="S15" s="15">
         <f>(1+IFERROR(VLOOKUP(E15,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F15,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G15,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H15,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I15,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J15,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K15,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L15,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M15,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N15,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O15,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -2330,10 +2684,30 @@
         <f t="shared" si="5"/>
         <v>7186.1984591418732</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB15" s="16">
+        <f t="shared" si="6"/>
+        <v>0.366771618949989</v>
+      </c>
+      <c r="AC15" s="16">
+        <f t="shared" si="7"/>
+        <v>0.52619158374034358</v>
+      </c>
+      <c r="AD15" s="16">
+        <f t="shared" si="8"/>
+        <v>261.3</v>
+      </c>
+      <c r="AE15" s="14">
+        <f t="shared" si="9"/>
+        <v>5009</v>
+      </c>
+      <c r="AF15" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="16.5" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B16" s="10">
         <v>1990</v>
@@ -2346,46 +2720,46 @@
         <v>6392</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P16" s="10">
         <v>6699</v>
       </c>
-      <c r="Q16" s="15">
-        <f t="shared" si="6"/>
-        <v>7.784743345731604</v>
-      </c>
-      <c r="R16" s="15">
+      <c r="Q16" s="16">
+        <f t="shared" si="11"/>
+        <v>7.7847433457316262</v>
+      </c>
+      <c r="R16" s="16">
         <f t="shared" si="1"/>
         <v>289.46210651598869</v>
       </c>
@@ -2425,10 +2799,30 @@
         <f t="shared" si="5"/>
         <v>7745.6255655009872</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB16" s="16">
+        <f t="shared" si="6"/>
+        <v>0.40902101486417219</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="7"/>
+        <v>0.56715424804136971</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="8"/>
+        <v>289.5</v>
+      </c>
+      <c r="AE16" s="14">
+        <f t="shared" si="9"/>
+        <v>5586</v>
+      </c>
+      <c r="AF16" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="16.5" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" s="10">
         <v>2100</v>
@@ -2441,48 +2835,48 @@
         <v>6393</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P17" s="10">
         <v>7667</v>
       </c>
-      <c r="Q17" s="15">
-        <f t="shared" si="6"/>
+      <c r="Q17" s="16">
+        <f t="shared" si="11"/>
         <v>5.0665177344110246</v>
       </c>
-      <c r="R17" s="15">
+      <c r="R17" s="16">
         <f t="shared" si="1"/>
-        <v>309.19427321143201</v>
+        <v>309.19427321143206</v>
       </c>
       <c r="S17" s="15">
         <f>(1+IFERROR(VLOOKUP(E17,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F17,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G17,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H17,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I17,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J17,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K17,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L17,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M17,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N17,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O17,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -2520,10 +2914,30 @@
         <f t="shared" si="5"/>
         <v>8138.0590584181682</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB17" s="16">
+        <f t="shared" si="6"/>
+        <v>0.44453393863952551</v>
+      </c>
+      <c r="AC17" s="16">
+        <f t="shared" si="7"/>
+        <v>0.59588921859985133</v>
+      </c>
+      <c r="AD17" s="16">
+        <f t="shared" si="8"/>
+        <v>309.2</v>
+      </c>
+      <c r="AE17" s="14">
+        <f t="shared" si="9"/>
+        <v>6071</v>
+      </c>
+      <c r="AF17" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="16.5" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B18" s="10">
         <v>2185</v>
@@ -2536,48 +2950,48 @@
         <v>6396</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P18" s="10">
         <v>8635</v>
       </c>
-      <c r="Q18" s="15">
-        <f t="shared" si="6"/>
-        <v>18.925265615177178</v>
-      </c>
-      <c r="R18" s="15">
+      <c r="Q18" s="16">
+        <f t="shared" si="11"/>
+        <v>18.925265615177199</v>
+      </c>
+      <c r="R18" s="16">
         <f t="shared" si="1"/>
-        <v>386.63537629878925</v>
+        <v>386.63537629878942</v>
       </c>
       <c r="S18" s="15">
         <f>(1+IFERROR(VLOOKUP(E18,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F18,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G18,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H18,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I18,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J18,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K18,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L18,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M18,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N18,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O18,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -2615,10 +3029,30 @@
         <f t="shared" si="5"/>
         <v>9678.2083511437941</v>
       </c>
-    </row>
-    <row r="19" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB18" s="16">
+        <f t="shared" si="6"/>
+        <v>0.54675258109394453</v>
+      </c>
+      <c r="AC18" s="16">
+        <f t="shared" si="7"/>
+        <v>0.70866283599207691</v>
+      </c>
+      <c r="AD18" s="16">
+        <f t="shared" si="8"/>
+        <v>386.6</v>
+      </c>
+      <c r="AE18" s="14">
+        <f t="shared" si="9"/>
+        <v>7467</v>
+      </c>
+      <c r="AF18" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" ht="16.5" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B19" s="10">
         <v>2270</v>
@@ -2631,48 +3065,48 @@
         <v>6399</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P19" s="10">
         <v>9603</v>
       </c>
-      <c r="Q19" s="15">
-        <f t="shared" si="6"/>
+      <c r="Q19" s="16">
+        <f t="shared" si="11"/>
         <v>6.5156084682436388</v>
       </c>
-      <c r="R19" s="15">
+      <c r="R19" s="16">
         <f t="shared" si="1"/>
-        <v>418.34263208638259</v>
+        <v>418.34263208638271</v>
       </c>
       <c r="S19" s="15">
         <f>(1+IFERROR(VLOOKUP(E19,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F19,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G19,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H19,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I19,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J19,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K19,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L19,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M19,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N19,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O19,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -2696,7 +3130,7 @@
       </c>
       <c r="X19" s="16">
         <f t="shared" si="2"/>
-        <v>0.82242243410642968</v>
+        <v>0.82242243410642957</v>
       </c>
       <c r="Y19" s="16">
         <f t="shared" si="3"/>
@@ -2708,12 +3142,32 @@
       </c>
       <c r="AA19" s="15">
         <f t="shared" si="5"/>
-        <v>10308.802514045183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="16.5" customHeight="1">
+        <v>10308.802514045185</v>
+      </c>
+      <c r="AB19" s="16">
+        <f t="shared" si="6"/>
+        <v>0.6021820311927949</v>
+      </c>
+      <c r="AC19" s="16">
+        <f t="shared" si="7"/>
+        <v>0.75483653174527243</v>
+      </c>
+      <c r="AD19" s="16">
+        <f t="shared" si="8"/>
+        <v>418.3</v>
+      </c>
+      <c r="AE19" s="14">
+        <f t="shared" si="9"/>
+        <v>8224</v>
+      </c>
+      <c r="AF19" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="16.5" customHeight="1">
       <c r="A20" s="10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B20" s="10">
         <v>2355</v>
@@ -2726,46 +3180,46 @@
         <v>6451</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P20" s="10">
         <v>10087</v>
       </c>
-      <c r="Q20" s="15">
-        <f t="shared" si="6"/>
-        <v>5.2889435745421931</v>
-      </c>
-      <c r="R20" s="15">
+      <c r="Q20" s="16">
+        <f t="shared" si="11"/>
+        <v>5.2889435745421709</v>
+      </c>
+      <c r="R20" s="16">
         <f t="shared" si="1"/>
         <v>445.75748142022815</v>
       </c>
@@ -2805,10 +3259,30 @@
         <f t="shared" si="5"/>
         <v>10854.029262224019</v>
       </c>
-    </row>
-    <row r="21" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB20" s="16">
+        <f t="shared" si="6"/>
+        <v>0.64494398476971515</v>
+      </c>
+      <c r="AC20" s="16">
+        <f t="shared" si="7"/>
+        <v>0.79475940998931083</v>
+      </c>
+      <c r="AD20" s="16">
+        <f t="shared" si="8"/>
+        <v>445.8</v>
+      </c>
+      <c r="AE20" s="14">
+        <f t="shared" si="9"/>
+        <v>8808</v>
+      </c>
+      <c r="AF20" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="16.5" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B21" s="10">
         <v>2440</v>
@@ -2821,48 +3295,48 @@
         <v>6452</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P21" s="10">
         <v>11167</v>
       </c>
-      <c r="Q21" s="15">
-        <f t="shared" si="6"/>
+      <c r="Q21" s="16">
+        <f t="shared" si="11"/>
         <v>9.9537778359643845</v>
       </c>
-      <c r="R21" s="15">
+      <c r="R21" s="16">
         <f t="shared" si="1"/>
-        <v>500.08096864395225</v>
+        <v>500.0809686439523</v>
       </c>
       <c r="S21" s="15">
         <f>(1+IFERROR(VLOOKUP(E21,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F21,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G21,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H21,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I21,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J21,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K21,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L21,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M21,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N21,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O21,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
@@ -2900,10 +3374,30 @@
         <f t="shared" si="5"/>
         <v>11934.415221236362</v>
       </c>
-    </row>
-    <row r="22" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB21" s="16">
+        <f t="shared" si="6"/>
+        <v>0.76122135168777916</v>
+      </c>
+      <c r="AC21" s="16">
+        <f t="shared" si="7"/>
+        <v>0.87386799599006837</v>
+      </c>
+      <c r="AD21" s="16">
+        <f t="shared" si="8"/>
+        <v>500.1</v>
+      </c>
+      <c r="AE21" s="14">
+        <f t="shared" si="9"/>
+        <v>10396</v>
+      </c>
+      <c r="AF21" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="16.5" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B22" s="10">
         <v>2550</v>
@@ -2916,46 +3410,46 @@
         <v>6453</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P22" s="10">
         <v>11707</v>
       </c>
-      <c r="Q22" s="15">
-        <f t="shared" si="6"/>
+      <c r="Q22" s="16">
+        <f t="shared" si="11"/>
         <v>12.048017019565926</v>
       </c>
-      <c r="R22" s="15">
+      <c r="R22" s="16">
         <f t="shared" si="1"/>
         <v>572.37882587735169</v>
       </c>
@@ -2995,8 +3489,28 @@
         <f t="shared" si="5"/>
         <v>13372.275598276585</v>
       </c>
-    </row>
-    <row r="23" spans="1:27">
+      <c r="AB22" s="16">
+        <f t="shared" si="6"/>
+        <v>0.92487369114739693</v>
+      </c>
+      <c r="AC22" s="16">
+        <f t="shared" si="7"/>
+        <v>0.97915176087549138</v>
+      </c>
+      <c r="AD22" s="16">
+        <f t="shared" si="8"/>
+        <v>572.4</v>
+      </c>
+      <c r="AE22" s="14">
+        <f t="shared" si="9"/>
+        <v>12631</v>
+      </c>
+      <c r="AF22" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -3025,53 +3539,59 @@
       <c r="Z23" s="10"/>
       <c r="AA23" s="10"/>
     </row>
-    <row r="24" spans="1:27" ht="16.5" customHeight="1">
+    <row r="24" spans="1:32" ht="16.5" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="10"/>
+        <v>58</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="C24" s="10" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O24" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
+      <c r="Q24" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R24" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
       <c r="U24" s="10"/>
@@ -3082,11 +3602,14 @@
       <c r="Z24" s="10"/>
       <c r="AA24" s="10"/>
     </row>
-    <row r="25" spans="1:27" ht="16.5" customHeight="1">
+    <row r="25" spans="1:32" ht="16.5" customHeight="1">
       <c r="A25" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="10"/>
+        <v>64</v>
+      </c>
+      <c r="B25" s="10">
+        <f>IFERROR(VLOOKUP(E25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(F25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(G25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(H25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(I25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(J25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(K25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(L25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(M25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(N25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)+IFERROR(VLOOKUP(O25,'장비 등급별 옵션'!$A$43:$B$48,2,FALSE),0)</f>
+        <v>2615</v>
+      </c>
       <c r="C25" s="10">
         <v>13657</v>
       </c>
@@ -3094,43 +3617,47 @@
         <v>6453</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P25" s="10">
         <v>11707</v>
       </c>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
+      <c r="Q25" s="10">
+        <v>779</v>
+      </c>
+      <c r="R25" s="10">
+        <v>4</v>
+      </c>
       <c r="S25" s="15">
         <f>(1+IFERROR(VLOOKUP(E25,'장비 등급별 옵션'!$A$2:$D$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(F25,'장비 등급별 옵션'!$A$9:$D$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(G25,'장비 등급별 옵션'!$A$16:$D$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(H25,'장비 등급별 옵션'!$A$23:$D$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(I25,'장비 등급별 옵션'!$A$30:$D$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(J25,'장비 등급별 옵션'!$J$2:$N$6,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(K25,'장비 등급별 옵션'!$J$9:$N$13,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(L25,'장비 등급별 옵션'!$J$16:$N$20,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(M25,'장비 등급별 옵션'!$J$23:$N$27,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(N25,'장비 등급별 옵션'!$J$30:$N$34,3,FALSE),0)/100)*(1+IFERROR(VLOOKUP(O25,'장비 등급별 옵션'!$J$37:$N$40,3,FALSE),0)/100)</f>
         <v>133.53254865875803</v>
@@ -3152,33 +3679,54 @@
         <v>1719</v>
       </c>
       <c r="X25" s="16">
-        <f>(S25*((1.05+U25*0.0045)/(1.05))*IF(V25&gt;=100,1E+99,100/(100-V25)))/($S$25*((1.05+$U$25*0.0045)/(1.05))*IF($V$25&gt;=100,1E+99,100/(100-$V$25)))</f>
+        <f>1</f>
         <v>1</v>
       </c>
       <c r="Y25" s="16">
-        <f>IF($C$27="",1,(1+($C$27+T25-$T$25)/100)/(1+$C$27/100))</f>
+        <f>1</f>
         <v>1</v>
       </c>
       <c r="Z25" s="16">
-        <f>IF($D$25="","",(1+($D$25+168350+297900+INT(3.08*($D$25-779)+2886))/250)/(1+($D$25+168350+297900+INT(3.08*($D$25-779)+2886))/250))</f>
+        <f>1</f>
         <v>1</v>
       </c>
       <c r="AA25" s="15">
-        <f>IF(Z25="","",C25/X25/Y25/Z25)</f>
+        <f>C25</f>
         <v>13657</v>
       </c>
-    </row>
-    <row r="26" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB25" s="15">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="AC25" s="15">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="AD25" s="15">
+        <f>IF(OR(AC25="",$AC$2="",$R$25=""),"",ROUND((AC25/$AC$2*(1+$R$25/100)-1)*100,1))</f>
+        <v>586.70000000000005</v>
+      </c>
+      <c r="AE25" s="15">
+        <f>C25</f>
+        <v>13657</v>
+      </c>
+      <c r="AF25" s="15">
+        <f>0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" ht="16.5" customHeight="1">
       <c r="C26" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32">
       <c r="C27" s="10">
         <v>71104</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AF22" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations xWindow="446" yWindow="320" count="22">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="목록에서 선택" error="장비 등급별 옵션 시트에 있는 등급만 선택할 수 있습니다." promptTitle="장비 등급 선택" prompt="드롭다운에서 등급을 선택하세요." sqref="E25" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3249,6 +3797,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3277,57 +3826,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B2" s="10">
         <v>750</v>
@@ -3339,7 +3888,7 @@
         <v>760</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" s="10">
         <v>11</v>
@@ -3379,7 +3928,7 @@
     </row>
     <row r="3" spans="1:17" ht="16.5" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" s="10">
         <v>830</v>
@@ -3391,7 +3940,7 @@
         <v>830</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F3" s="10">
         <v>11</v>
@@ -3431,7 +3980,7 @@
     </row>
     <row r="4" spans="1:17" ht="16.5" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" s="10">
         <v>910</v>
@@ -3443,7 +3992,7 @@
         <v>910</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F4" s="10">
         <v>11</v>
@@ -3483,7 +4032,7 @@
     </row>
     <row r="5" spans="1:17" ht="16.5" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B5" s="10">
         <v>990</v>
@@ -3495,7 +4044,7 @@
         <v>990</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F5" s="10">
         <v>11</v>
@@ -3535,7 +4084,7 @@
     </row>
     <row r="6" spans="1:17" ht="16.5" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6" s="10">
         <v>1070</v>
@@ -3547,7 +4096,7 @@
         <v>1070</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F6" s="10">
         <v>11</v>
@@ -3587,7 +4136,7 @@
     </row>
     <row r="7" spans="1:17" ht="16.5" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" s="10">
         <v>1200</v>
@@ -3599,7 +4148,7 @@
         <v>1200</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10">
@@ -3639,7 +4188,7 @@
     </row>
     <row r="8" spans="1:17" ht="16.5" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" s="10">
         <v>1285</v>
@@ -3651,7 +4200,7 @@
         <v>1290</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10">
@@ -3691,7 +4240,7 @@
     </row>
     <row r="9" spans="1:17" ht="16.5" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" s="10">
         <v>1370</v>
@@ -3703,7 +4252,7 @@
         <v>1370</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10">
@@ -3743,7 +4292,7 @@
     </row>
     <row r="10" spans="1:17" ht="16.5" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B10" s="10">
         <v>1455</v>
@@ -3755,7 +4304,7 @@
         <v>1460</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="10">
@@ -3795,7 +4344,7 @@
     </row>
     <row r="11" spans="1:17" ht="16.5" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B11" s="10">
         <v>1540</v>
@@ -3807,7 +4356,7 @@
         <v>1540</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="10">
@@ -3847,7 +4396,7 @@
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B12" s="10">
         <v>1650</v>
@@ -3859,7 +4408,7 @@
         <v>1650</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10">
@@ -3901,7 +4450,7 @@
     </row>
     <row r="13" spans="1:17" ht="16.5" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B13" s="10">
         <v>1735</v>
@@ -3913,7 +4462,7 @@
         <v>1740</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -3953,7 +4502,7 @@
     </row>
     <row r="14" spans="1:17" ht="16.5" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B14" s="10">
         <v>1820</v>
@@ -3965,7 +4514,7 @@
         <v>1820</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -4005,7 +4554,7 @@
     </row>
     <row r="15" spans="1:17" ht="16.5" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B15" s="10">
         <v>1905</v>
@@ -4017,7 +4566,7 @@
         <v>1910</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -4057,7 +4606,7 @@
     </row>
     <row r="16" spans="1:17" ht="16.5" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B16" s="10">
         <v>1990</v>
@@ -4069,7 +4618,7 @@
         <v>1990</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -4109,7 +4658,7 @@
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" s="10">
         <v>2100</v>
@@ -4121,7 +4670,7 @@
         <v>2100</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
@@ -4163,7 +4712,7 @@
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B18" s="10">
         <v>2185</v>
@@ -4175,7 +4724,7 @@
         <v>2190</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -4219,7 +4768,7 @@
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B19" s="10">
         <v>2270</v>
@@ -4231,7 +4780,7 @@
         <v>2270</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
@@ -4273,7 +4822,7 @@
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1">
       <c r="A20" s="10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B20" s="10">
         <v>2355</v>
@@ -4285,7 +4834,7 @@
         <v>2360</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -4327,7 +4876,7 @@
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B21" s="10">
         <v>2440</v>
@@ -4339,7 +4888,7 @@
         <v>2440</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
@@ -4381,7 +4930,7 @@
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B22" s="10">
         <v>2550</v>
@@ -4393,7 +4942,7 @@
         <v>2550</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -4454,35 +5003,35 @@
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D24" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>58</v>
-      </c>
       <c r="F24" s="10" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="L24" s="10"/>
       <c r="M24" s="10"/>
@@ -4493,7 +5042,7 @@
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1">
       <c r="A25" s="10" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10">
@@ -4503,7 +5052,7 @@
         <v>2440</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F25" s="10">
         <v>6679</v>
@@ -4542,7 +5091,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5396DAC0-911E-4B23-BA8B-39ACE2B3B916}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4552,38 +5101,38 @@
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" customHeight="1">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>7439</v>
@@ -4592,7 +5141,7 @@
         <v>760</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E2" s="4">
         <f>0</f>
@@ -4615,9 +5164,9 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5">
+    <row r="3" spans="1:9" ht="16.5" customHeight="1">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>7534</v>
@@ -4626,7 +5175,7 @@
         <v>830</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E3" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4649,9 +5198,9 @@
         <v>1.1850000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>7630</v>
@@ -4660,7 +5209,7 @@
         <v>910</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E4" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4683,9 +5232,9 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.5">
+    <row r="5" spans="1:9" ht="16.5" customHeight="1">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>7725</v>
@@ -4694,7 +5243,7 @@
         <v>990</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E5" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4717,9 +5266,9 @@
         <v>1.2150000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5">
+    <row r="6" spans="1:9" ht="16.5" customHeight="1">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>7820</v>
@@ -4728,7 +5277,7 @@
         <v>1070</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E6" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4751,9 +5300,9 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.5">
+    <row r="7" spans="1:9" ht="16.5" customHeight="1">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>16477</v>
@@ -4762,7 +5311,7 @@
         <v>1200</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E7" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4785,9 +5334,9 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5">
+    <row r="8" spans="1:9" ht="16.5" customHeight="1">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>20179</v>
@@ -4796,7 +5345,7 @@
         <v>1290</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E8" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4819,9 +5368,9 @@
         <v>1.2949999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.5">
+    <row r="9" spans="1:9" ht="16.5" customHeight="1">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>23235</v>
@@ -4830,7 +5379,7 @@
         <v>1370</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E9" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4853,9 +5402,9 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.5">
+    <row r="10" spans="1:9" ht="16.5" customHeight="1">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>26448</v>
@@ -4864,7 +5413,7 @@
         <v>1460</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E10" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4887,9 +5436,9 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="16.5">
+    <row r="11" spans="1:9" ht="16.5" customHeight="1">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>29626</v>
@@ -4898,7 +5447,7 @@
         <v>1540</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E11" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4921,9 +5470,9 @@
         <v>1.345</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.5">
+    <row r="12" spans="1:9" ht="16.5" customHeight="1">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>38681</v>
@@ -4932,7 +5481,7 @@
         <v>1650</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E12" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4955,9 +5504,9 @@
         <v>1.3900000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16.5">
+    <row r="13" spans="1:9" ht="16.5" customHeight="1">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>52879</v>
@@ -4966,7 +5515,7 @@
         <v>1740</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E13" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -4989,9 +5538,9 @@
         <v>1.405</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16.5">
+    <row r="14" spans="1:9" ht="16.5" customHeight="1">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>58464</v>
@@ -5000,7 +5549,7 @@
         <v>1820</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E14" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5023,9 +5572,9 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="16.5">
+    <row r="15" spans="1:9" ht="16.5" customHeight="1">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>64395</v>
@@ -5034,7 +5583,7 @@
         <v>1910</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E15" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5057,9 +5606,9 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16.5">
+    <row r="16" spans="1:9" ht="16.5" customHeight="1">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>70249</v>
@@ -5068,7 +5617,7 @@
         <v>1990</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E16" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5091,9 +5640,9 @@
         <v>1.4550000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="16.5">
+    <row r="17" spans="1:9" ht="16.5" customHeight="1">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>91713</v>
@@ -5102,7 +5651,7 @@
         <v>2100</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E17" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5125,9 +5674,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.5">
+    <row r="18" spans="1:9" ht="16.5" customHeight="1">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>119877</v>
@@ -5136,7 +5685,7 @@
         <v>2190</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E18" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5159,9 +5708,9 @@
         <v>1.5150000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="16.5">
+    <row r="19" spans="1:9" ht="16.5" customHeight="1">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>134344</v>
@@ -5170,7 +5719,7 @@
         <v>2270</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E19" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5193,9 +5742,9 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16.5">
+    <row r="20" spans="1:9" ht="16.5" customHeight="1">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <v>146448</v>
@@ -5204,7 +5753,7 @@
         <v>2360</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E20" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5227,9 +5776,9 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16.5">
+    <row r="21" spans="1:9" ht="16.5" customHeight="1">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>158269</v>
@@ -5238,7 +5787,7 @@
         <v>2440</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E21" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5261,9 +5810,9 @@
         <v>1.5649999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16.5">
+    <row r="22" spans="1:9" ht="16.5" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>193306</v>
@@ -5272,7 +5821,7 @@
         <v>2550</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E22" s="4" t="e">
         <f>(#REF!/#REF!-1)*100</f>
@@ -5302,7 +5851,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5319,60 +5868,60 @@
   <sheetData>
     <row r="1" spans="1:18" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>2100</v>
@@ -5393,7 +5942,7 @@
         <v>140</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K2">
         <v>2100</v>
@@ -5419,7 +5968,7 @@
     </row>
     <row r="3" spans="1:18" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>3189</v>
@@ -5440,7 +5989,7 @@
         <v>142</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K3">
         <v>3189</v>
@@ -5466,7 +6015,7 @@
     </row>
     <row r="4" spans="1:18" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>3189</v>
@@ -5487,7 +6036,7 @@
         <v>143</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K4">
         <v>3189</v>
@@ -5513,7 +6062,7 @@
     </row>
     <row r="5" spans="1:18" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>3189</v>
@@ -5534,7 +6083,7 @@
         <v>144</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K5">
         <v>3189</v>
@@ -5560,7 +6109,7 @@
     </row>
     <row r="6" spans="1:18" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>3189</v>
@@ -5581,7 +6130,7 @@
         <v>144</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K6">
         <v>3189</v>
@@ -5607,60 +6156,60 @@
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>2100</v>
@@ -5681,7 +6230,7 @@
         <v>132</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K9">
         <v>2100</v>
@@ -5707,7 +6256,7 @@
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B10">
         <v>3189</v>
@@ -5728,7 +6277,7 @@
         <v>133</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K10">
         <v>3189</v>
@@ -5754,7 +6303,7 @@
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>3189</v>
@@ -5775,7 +6324,7 @@
         <v>134</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K11">
         <v>3189</v>
@@ -5801,7 +6350,7 @@
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>3189</v>
@@ -5822,7 +6371,7 @@
         <v>135</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K12">
         <v>3189</v>
@@ -5848,7 +6397,7 @@
     </row>
     <row r="13" spans="1:18" ht="16.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B13">
         <v>3189</v>
@@ -5869,7 +6418,7 @@
         <v>135</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K13">
         <v>3189</v>
@@ -5895,60 +6444,60 @@
     </row>
     <row r="15" spans="1:18" ht="16.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>2100</v>
@@ -5969,7 +6518,7 @@
         <v>140</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K16">
         <v>2100</v>
@@ -5995,7 +6544,7 @@
     </row>
     <row r="17" spans="1:18" ht="16.5" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>3189</v>
@@ -6016,7 +6565,7 @@
         <v>142</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K17">
         <v>3189</v>
@@ -6042,7 +6591,7 @@
     </row>
     <row r="18" spans="1:18" ht="16.5" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B18">
         <v>3189</v>
@@ -6063,7 +6612,7 @@
         <v>143</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K18">
         <v>3189</v>
@@ -6089,7 +6638,7 @@
     </row>
     <row r="19" spans="1:18" ht="16.5" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>3189</v>
@@ -6110,7 +6659,7 @@
         <v>144</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K19">
         <v>3189</v>
@@ -6136,7 +6685,7 @@
     </row>
     <row r="20" spans="1:18" ht="16.5" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B20">
         <v>3189</v>
@@ -6157,7 +6706,7 @@
         <v>144</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K20">
         <v>3189</v>
@@ -6183,60 +6732,60 @@
     </row>
     <row r="22" spans="1:18" ht="16.5" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="16.5" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B23">
         <v>2100</v>
@@ -6257,7 +6806,7 @@
         <v>124</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K23">
         <v>2100</v>
@@ -6280,7 +6829,7 @@
     </row>
     <row r="24" spans="1:18" ht="16.5" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>3189</v>
@@ -6301,7 +6850,7 @@
         <v>125</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K24">
         <v>3189</v>
@@ -6324,7 +6873,7 @@
     </row>
     <row r="25" spans="1:18" ht="16.5" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B25">
         <v>3189</v>
@@ -6345,7 +6894,7 @@
         <v>126</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K25">
         <v>3189</v>
@@ -6368,7 +6917,7 @@
     </row>
     <row r="26" spans="1:18" ht="16.5" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B26">
         <v>3189</v>
@@ -6389,7 +6938,7 @@
         <v>127</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K26">
         <v>3189</v>
@@ -6412,7 +6961,7 @@
     </row>
     <row r="27" spans="1:18" ht="16.5" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B27">
         <v>3189</v>
@@ -6436,60 +6985,60 @@
     </row>
     <row r="29" spans="1:18" ht="16.5" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="16.5" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>2100</v>
@@ -6510,7 +7059,7 @@
         <v>124</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K30">
         <v>2100</v>
@@ -6536,7 +7085,7 @@
     </row>
     <row r="31" spans="1:18" ht="16.5" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>3189</v>
@@ -6557,7 +7106,7 @@
         <v>125</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K31">
         <v>3189</v>
@@ -6583,7 +7132,7 @@
     </row>
     <row r="32" spans="1:18" ht="16.5" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B32">
         <v>3189</v>
@@ -6604,7 +7153,7 @@
         <v>126</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K32">
         <v>3189</v>
@@ -6630,7 +7179,7 @@
     </row>
     <row r="33" spans="1:18" ht="16.5" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B33">
         <v>3189</v>
@@ -6651,7 +7200,7 @@
         <v>127</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K33">
         <v>3189</v>
@@ -6677,7 +7226,7 @@
     </row>
     <row r="34" spans="1:18" ht="16.5" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B34">
         <v>3189</v>
@@ -6701,36 +7250,36 @@
     </row>
     <row r="36" spans="1:18" ht="16.5" customHeight="1">
       <c r="J36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="16.5" customHeight="1">
       <c r="J37" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K37">
         <v>2100</v>
@@ -6753,7 +7302,7 @@
     </row>
     <row r="38" spans="1:18" ht="16.5" customHeight="1">
       <c r="J38" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K38">
         <v>3189</v>
@@ -6776,7 +7325,7 @@
     </row>
     <row r="39" spans="1:18" ht="16.5" customHeight="1">
       <c r="J39" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K39">
         <v>3189</v>
@@ -6799,7 +7348,7 @@
     </row>
     <row r="40" spans="1:18" ht="16.5" customHeight="1">
       <c r="J40" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K40">
         <v>3189</v>
@@ -6823,54 +7372,54 @@
     <row r="41" spans="1:18" ht="16.5" customHeight="1">
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="1:18" ht="16.5">
+    <row r="42" spans="1:18" ht="16.5" customHeight="1">
       <c r="B42" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="16.5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="16.5" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="B43">
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="16.5">
+    <row r="44" spans="1:18" ht="16.5" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="B44">
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="16.5">
+    <row r="45" spans="1:18" ht="16.5" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="B45">
         <v>165</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="16.5">
+    <row r="46" spans="1:18" ht="16.5" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>215</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="16.5">
+    <row r="47" spans="1:18" ht="16.5" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="B47">
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="16.5">
+    <row r="48" spans="1:18" ht="16.5" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="B48">
         <v>265</v>
@@ -6883,7 +7432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE005852-D39C-42F6-93CC-C63D5310ED5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
@@ -6893,7 +7442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6905,33 +7454,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2">
         <v>750</v>
@@ -6954,7 +7503,7 @@
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2">
         <v>1200</v>
@@ -6977,7 +7526,7 @@
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2">
         <v>1650</v>
@@ -7000,7 +7549,7 @@
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2">
         <v>2100</v>
@@ -7023,7 +7572,7 @@
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2">
         <v>2550</v>
@@ -7045,14 +7594,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:H6" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7064,21 +7613,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>38</v>
@@ -7092,7 +7641,7 @@
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>44</v>
@@ -7106,7 +7655,7 @@
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>50</v>
@@ -7120,7 +7669,7 @@
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B5">
         <v>57</v>
@@ -7139,7 +7688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7148,47 +7697,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -7198,7 +7747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7209,100 +7758,100 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C11" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:C11" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
